--- a/Stocks/PRIM.xlsx
+++ b/Stocks/PRIM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://academiafaedupt-my.sharepoint.com/personal/sbclemente_academiafa_edu_pt/Documents/Gigs/WorkingFolder/Finance_Shared/Stocks/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="255" documentId="8_{FA6B7711-D306-41EB-8C0B-C4B71D8C46EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DF3E543B-E731-435F-9B58-C97B2580A177}"/>
+  <xr:revisionPtr revIDLastSave="270" documentId="8_{FA6B7711-D306-41EB-8C0B-C4B71D8C46EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0A764B4A-4B69-4C4B-9E1F-A9E7734D45B7}"/>
   <bookViews>
-    <workbookView xWindow="-1635" yWindow="3390" windowWidth="18225" windowHeight="9480" activeTab="1" xr2:uid="{03BD2B21-D6A9-48AB-9137-57CD30A5D9F5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{03BD2B21-D6A9-48AB-9137-57CD30A5D9F5}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="65">
   <si>
     <t>Price</t>
   </si>
@@ -292,6 +292,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -611,7 +615,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{085C94D1-2984-4389-A51D-3D825ADE3F80}">
-  <dimension ref="K2:BJ20"/>
+  <dimension ref="K2:BJ26"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="12" max="12" width="9.375" bestFit="1" customWidth="1"/>
@@ -665,22 +669,27 @@
         <v>0</v>
       </c>
       <c r="L3" s="1">
-        <v>205</v>
+        <v>100</v>
       </c>
       <c r="M3" s="1">
-        <v>205</v>
+        <f>+L3*1.1</f>
+        <v>110.00000000000001</v>
       </c>
       <c r="N3" s="1">
-        <v>205</v>
+        <f t="shared" ref="N3:Q3" si="1">+M3*1.1</f>
+        <v>121.00000000000003</v>
       </c>
       <c r="O3" s="1">
-        <v>205</v>
+        <f t="shared" si="1"/>
+        <v>133.10000000000005</v>
       </c>
       <c r="P3" s="1">
-        <v>205</v>
+        <f t="shared" si="1"/>
+        <v>146.41000000000008</v>
       </c>
       <c r="Q3" s="1">
-        <v>205</v>
+        <f t="shared" si="1"/>
+        <v>161.0510000000001</v>
       </c>
       <c r="R3" s="1"/>
       <c r="S3" s="1"/>
@@ -713,19 +722,19 @@
         <v>55.284000000000006</v>
       </c>
       <c r="N4" s="1">
-        <f t="shared" ref="N4:Q4" si="1">+M4*1.02</f>
+        <f t="shared" ref="N4:Q4" si="2">+M4*1.02</f>
         <v>56.389680000000006</v>
       </c>
       <c r="O4" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>57.51747360000001</v>
       </c>
       <c r="P4" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>58.667823072000012</v>
       </c>
       <c r="Q4" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>59.841179533440013</v>
       </c>
       <c r="R4" s="1"/>
@@ -753,27 +762,27 @@
       </c>
       <c r="L5" s="1">
         <f>+L4*L3</f>
-        <v>11111</v>
+        <v>5420</v>
       </c>
       <c r="M5" s="1">
-        <f t="shared" ref="M5:Q5" si="2">+M4*M3</f>
-        <v>11333.220000000001</v>
+        <f t="shared" ref="M5:Q5" si="3">+M4*M3</f>
+        <v>6081.2400000000016</v>
       </c>
       <c r="N5" s="1">
-        <f t="shared" si="2"/>
-        <v>11559.884400000001</v>
+        <f t="shared" si="3"/>
+        <v>6823.1512800000019</v>
       </c>
       <c r="O5" s="1">
-        <f t="shared" si="2"/>
-        <v>11791.082088000003</v>
+        <f t="shared" si="3"/>
+        <v>7655.5757361600045</v>
       </c>
       <c r="P5" s="1">
-        <f t="shared" si="2"/>
-        <v>12026.903729760003</v>
+        <f t="shared" si="3"/>
+        <v>8589.555975971527</v>
       </c>
       <c r="Q5" s="1">
-        <f t="shared" si="2"/>
-        <v>12267.441804355203</v>
+        <f t="shared" si="3"/>
+        <v>9637.4818050400536</v>
       </c>
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
@@ -806,19 +815,19 @@
         <v>530.14499999999998</v>
       </c>
       <c r="N6" s="1">
-        <f t="shared" ref="N6:Q6" si="3">+M6*0.99</f>
+        <f t="shared" ref="N6:Q6" si="4">+M6*0.99</f>
         <v>524.84354999999994</v>
       </c>
       <c r="O6" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>519.59511449999991</v>
       </c>
       <c r="P6" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>514.39916335499993</v>
       </c>
       <c r="Q6" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>509.25517172144993</v>
       </c>
       <c r="R6" s="1"/>
@@ -853,19 +862,19 @@
         <v>483.99700000000001</v>
       </c>
       <c r="N7" s="1">
-        <f t="shared" ref="N7:Q7" si="4">+M7*1.03</f>
+        <f t="shared" ref="N7:Q7" si="5">+M7*1.03</f>
         <v>498.51691000000005</v>
       </c>
       <c r="O7" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>513.47241730000007</v>
       </c>
       <c r="P7" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>528.87658981900006</v>
       </c>
       <c r="Q7" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>544.74288751357005</v>
       </c>
       <c r="R7" s="1"/>
@@ -893,27 +902,27 @@
       </c>
       <c r="L8" s="1">
         <f>+L5-L6+L7</f>
-        <v>11045.4</v>
+        <v>5354.4</v>
       </c>
       <c r="M8" s="1">
-        <f t="shared" ref="M8:Q8" si="5">+M5-M6+M7</f>
-        <v>11287.072</v>
+        <f t="shared" ref="M8:Q8" si="6">+M5-M6+M7</f>
+        <v>6035.0920000000015</v>
       </c>
       <c r="N8" s="1">
-        <f t="shared" si="5"/>
-        <v>11533.557760000002</v>
+        <f t="shared" si="6"/>
+        <v>6796.8246400000025</v>
       </c>
       <c r="O8" s="1">
-        <f t="shared" si="5"/>
-        <v>11784.959390800002</v>
+        <f t="shared" si="6"/>
+        <v>7649.453038960005</v>
       </c>
       <c r="P8" s="1">
-        <f t="shared" si="5"/>
-        <v>12041.381156224003</v>
+        <f t="shared" si="6"/>
+        <v>8604.033402435527</v>
       </c>
       <c r="Q8" s="1">
-        <f t="shared" si="5"/>
-        <v>12302.929520147323</v>
+        <f t="shared" si="6"/>
+        <v>9672.9695208321737</v>
       </c>
       <c r="R8" s="1"/>
       <c r="S8" s="1"/>
@@ -937,7 +946,7 @@
     <row r="9" spans="11:62" x14ac:dyDescent="0.2">
       <c r="K9" s="1"/>
       <c r="L9" s="1">
-        <v>-11045</v>
+        <v>-5354</v>
       </c>
       <c r="M9" s="1">
         <v>0</v>
@@ -953,7 +962,7 @@
       </c>
       <c r="Q9" s="1">
         <f>+Q8</f>
-        <v>12302.929520147323</v>
+        <v>9672.9695208321737</v>
       </c>
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
@@ -1048,7 +1057,7 @@
         <v>343.62499999999943</v>
       </c>
       <c r="N12" s="1">
-        <f t="shared" ref="N12" si="6">+M12*1.25</f>
+        <f t="shared" ref="N12" si="7">+M12*1.25</f>
         <v>429.53124999999932</v>
       </c>
       <c r="O12" s="1">
@@ -1056,7 +1065,7 @@
         <v>515.4374999999992</v>
       </c>
       <c r="P12" s="1">
-        <f t="shared" ref="P12" si="7">+O12*1.2</f>
+        <f t="shared" ref="P12" si="8">+O12*1.2</f>
         <v>618.52499999999907</v>
       </c>
       <c r="Q12" s="1">
@@ -1068,71 +1077,71 @@
         <v>697.07767499999886</v>
       </c>
       <c r="S12" s="1">
-        <f t="shared" ref="S12:AI12" si="8">+R12*0.98</f>
+        <f t="shared" ref="S12:AI12" si="9">+R12*0.98</f>
         <v>683.13612149999892</v>
       </c>
       <c r="T12" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>669.47339906999889</v>
       </c>
       <c r="U12" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>656.08393108859889</v>
       </c>
       <c r="V12" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>642.96225246682695</v>
       </c>
       <c r="W12" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>630.1030074174904</v>
       </c>
       <c r="X12" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>617.50094726914062</v>
       </c>
       <c r="Y12" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>605.15092832375785</v>
       </c>
       <c r="Z12" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>593.0479097572827</v>
       </c>
       <c r="AA12" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>581.18695156213698</v>
       </c>
       <c r="AB12" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>569.56321253089425</v>
       </c>
       <c r="AC12" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>558.1719482802763</v>
       </c>
       <c r="AD12" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>547.00850931467073</v>
       </c>
       <c r="AE12" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>536.06833912837726</v>
       </c>
       <c r="AF12" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>525.34697234580972</v>
       </c>
       <c r="AG12" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>514.84003289889347</v>
       </c>
       <c r="AH12" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>504.54323224091559</v>
       </c>
       <c r="AI12" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>494.45236759609725</v>
       </c>
       <c r="BJ12" t="s">
@@ -1143,23 +1152,23 @@
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1">
-        <f t="shared" ref="M13:Q13" si="9">+M12/L12-1</f>
+        <f t="shared" ref="M13:Q13" si="10">+M12/L12-1</f>
         <v>0.25</v>
       </c>
       <c r="N13" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.25</v>
       </c>
       <c r="O13" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.19999999999999996</v>
       </c>
       <c r="P13" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.19999999999999996</v>
       </c>
       <c r="Q13" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.14999999999999991</v>
       </c>
       <c r="R13" s="1"/>
@@ -1187,27 +1196,27 @@
       </c>
       <c r="L14" s="1">
         <f>+L8/L12</f>
-        <v>40.179701709712688</v>
+        <v>19.47762822844674</v>
       </c>
       <c r="M14" s="1">
-        <f t="shared" ref="M14:Q14" si="10">+M8/M12</f>
-        <v>32.847062931975316</v>
+        <f t="shared" ref="M14:Q14" si="11">+M8/M12</f>
+        <v>17.563017824663547</v>
       </c>
       <c r="N14" s="1">
-        <f t="shared" si="10"/>
-        <v>26.851498604583529</v>
+        <f t="shared" si="11"/>
+        <v>15.823818732630079</v>
       </c>
       <c r="O14" s="1">
-        <f t="shared" si="10"/>
-        <v>22.863992997793176</v>
+        <f t="shared" si="11"/>
+        <v>14.840699481430855</v>
       </c>
       <c r="P14" s="1">
-        <f t="shared" si="10"/>
-        <v>19.467897265630363</v>
+        <f t="shared" si="11"/>
+        <v>13.910566917158627</v>
       </c>
       <c r="Q14" s="1">
-        <f t="shared" si="10"/>
-        <v>17.296309094598957</v>
+        <f t="shared" si="11"/>
+        <v>13.598929459927898</v>
       </c>
       <c r="R14" s="1"/>
       <c r="S14" s="1"/>
@@ -1237,23 +1246,23 @@
         <v>5.0719557195571863</v>
       </c>
       <c r="M15" s="1">
-        <f t="shared" ref="M15:Q15" si="11">+M12/M4</f>
+        <f t="shared" ref="M15:Q15" si="12">+M12/M4</f>
         <v>6.2156320092612578</v>
       </c>
       <c r="N15" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>7.6171960897809541</v>
       </c>
       <c r="O15" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>8.9614071644481808</v>
       </c>
       <c r="P15" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>10.542831958174331</v>
       </c>
       <c r="Q15" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>11.886526227353412</v>
       </c>
       <c r="R15" s="1"/>
@@ -1281,27 +1290,27 @@
       </c>
       <c r="L16" s="1">
         <f>+L3/L15</f>
-        <v>40.418333939614477</v>
+        <v>19.716260458348525</v>
       </c>
       <c r="M16" s="1">
-        <f t="shared" ref="M16:Q16" si="12">+M3/M15</f>
-        <v>32.981360494725415</v>
+        <f t="shared" ref="M16:Q16" si="13">+M3/M15</f>
+        <v>17.697315387413639</v>
       </c>
       <c r="N16" s="1">
-        <f t="shared" si="12"/>
-        <v>26.912790163695934</v>
+        <f t="shared" si="13"/>
+        <v>15.885110291742482</v>
       </c>
       <c r="O16" s="1">
-        <f t="shared" si="12"/>
-        <v>22.875871639141547</v>
+        <f t="shared" si="13"/>
+        <v>14.852578122779224</v>
       </c>
       <c r="P16" s="1">
-        <f t="shared" si="12"/>
-        <v>19.444490893270313</v>
+        <f t="shared" si="13"/>
+        <v>13.887160544798578</v>
       </c>
       <c r="Q16" s="1">
-        <f t="shared" si="12"/>
-        <v>17.246418009683232</v>
+        <f t="shared" si="13"/>
+        <v>13.549038375012177</v>
       </c>
       <c r="R16" s="1"/>
       <c r="S16" s="1"/>
@@ -1322,16 +1331,16 @@
       <c r="AH16" s="1"/>
       <c r="AI16" s="1"/>
     </row>
-    <row r="18" spans="11:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="11:15" x14ac:dyDescent="0.2">
       <c r="K18" t="s">
         <v>60</v>
       </c>
       <c r="L18" s="2">
         <f>+IRR(L9:Q9)</f>
-        <v>2.180626977272504E-2</v>
-      </c>
-    </row>
-    <row r="19" spans="11:12" x14ac:dyDescent="0.2">
+        <v>0.1255797999507231</v>
+      </c>
+    </row>
+    <row r="19" spans="11:15" x14ac:dyDescent="0.2">
       <c r="K19" t="s">
         <v>61</v>
       </c>
@@ -1340,13 +1349,23 @@
         <v>5887.6398670054677</v>
       </c>
     </row>
-    <row r="20" spans="11:12" x14ac:dyDescent="0.2">
+    <row r="20" spans="11:15" x14ac:dyDescent="0.2">
       <c r="K20" t="s">
         <v>62</v>
       </c>
       <c r="L20">
         <f>+L19/L4</f>
         <v>108.62804182666915</v>
+      </c>
+    </row>
+    <row r="25" spans="11:15" x14ac:dyDescent="0.2">
+      <c r="O25" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" spans="11:15" x14ac:dyDescent="0.2">
+      <c r="O26" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -1450,6 +1469,10 @@
       <c r="J3">
         <v>1559.9</v>
       </c>
+      <c r="K3">
+        <f>+J3*4</f>
+        <v>6239.6</v>
+      </c>
       <c r="O3">
         <v>3491</v>
       </c>
@@ -1678,124 +1701,124 @@
         <v>274.89999999999952</v>
       </c>
       <c r="U12">
-        <f>+T12*1.25</f>
-        <v>343.62499999999943</v>
+        <f>+T12*1.05</f>
+        <v>288.64499999999953</v>
       </c>
       <c r="V12">
-        <f t="shared" ref="V12:W12" si="2">+U12*1.25</f>
-        <v>429.53124999999932</v>
+        <f t="shared" ref="V12:X12" si="2">+U12*1.05</f>
+        <v>303.07724999999954</v>
       </c>
       <c r="W12">
         <f t="shared" si="2"/>
-        <v>536.91406249999909</v>
+        <v>318.23111249999954</v>
       </c>
       <c r="X12">
-        <f>+W12*1.15</f>
-        <v>617.45117187499886</v>
+        <f t="shared" si="2"/>
+        <v>334.14266812499955</v>
       </c>
       <c r="Y12">
-        <f t="shared" ref="Y12:Z12" si="3">+X12*1.15</f>
-        <v>710.06884765624864</v>
+        <f>+X12</f>
+        <v>334.14266812499955</v>
       </c>
       <c r="Z12">
-        <f t="shared" si="3"/>
-        <v>816.57917480468586</v>
+        <f t="shared" ref="Z12" si="3">+Y12</f>
+        <v>334.14266812499955</v>
       </c>
       <c r="AA12">
         <f>+Z12*0.98</f>
-        <v>800.24759130859218</v>
+        <v>327.45981476249955</v>
       </c>
       <c r="AB12">
         <f t="shared" ref="AB12:AX12" si="4">+AA12*0.98</f>
-        <v>784.24263948242037</v>
+        <v>320.91061846724955</v>
       </c>
       <c r="AC12">
         <f t="shared" si="4"/>
-        <v>768.55778669277197</v>
+        <v>314.49240609790456</v>
       </c>
       <c r="AD12">
         <f t="shared" si="4"/>
-        <v>753.18663095891657</v>
+        <v>308.20255797594649</v>
       </c>
       <c r="AE12">
         <f t="shared" si="4"/>
-        <v>738.12289833973819</v>
+        <v>302.03850681642757</v>
       </c>
       <c r="AF12">
         <f t="shared" si="4"/>
-        <v>723.36044037294346</v>
+        <v>295.99773668009902</v>
       </c>
       <c r="AG12">
         <f t="shared" si="4"/>
-        <v>708.8932315654846</v>
+        <v>290.07778194649705</v>
       </c>
       <c r="AH12">
         <f t="shared" si="4"/>
-        <v>694.71536693417488</v>
+        <v>284.27622630756713</v>
       </c>
       <c r="AI12">
         <f t="shared" si="4"/>
-        <v>680.82105959549142</v>
+        <v>278.59070178141576</v>
       </c>
       <c r="AJ12">
         <f t="shared" si="4"/>
-        <v>667.20463840358161</v>
+        <v>273.01888774578742</v>
       </c>
       <c r="AK12">
         <f t="shared" si="4"/>
-        <v>653.86054563550999</v>
+        <v>267.5585099908717</v>
       </c>
       <c r="AL12">
         <f t="shared" si="4"/>
-        <v>640.78333472279974</v>
+        <v>262.20733979105427</v>
       </c>
       <c r="AM12">
         <f t="shared" si="4"/>
-        <v>627.96766802834372</v>
+        <v>256.96319299523316</v>
       </c>
       <c r="AN12">
         <f t="shared" si="4"/>
-        <v>615.40831466777684</v>
+        <v>251.82392913532848</v>
       </c>
       <c r="AO12">
         <f t="shared" si="4"/>
-        <v>603.10014837442134</v>
+        <v>246.78745055262192</v>
       </c>
       <c r="AP12">
         <f t="shared" si="4"/>
-        <v>591.03814540693293</v>
+        <v>241.85170154156947</v>
       </c>
       <c r="AQ12">
         <f t="shared" si="4"/>
-        <v>579.21738249879422</v>
+        <v>237.01466751073806</v>
       </c>
       <c r="AR12">
         <f t="shared" si="4"/>
-        <v>567.63303484881828</v>
+        <v>232.27437416052331</v>
       </c>
       <c r="AS12">
         <f t="shared" si="4"/>
-        <v>556.2803741518419</v>
+        <v>227.62888667731283</v>
       </c>
       <c r="AT12">
         <f t="shared" si="4"/>
-        <v>545.154766668805</v>
+        <v>223.07630894376658</v>
       </c>
       <c r="AU12">
         <f t="shared" si="4"/>
-        <v>534.25167133542891</v>
+        <v>218.61478276489123</v>
       </c>
       <c r="AV12">
         <f t="shared" si="4"/>
-        <v>523.56663790872028</v>
+        <v>214.24248710959341</v>
       </c>
       <c r="AW12">
         <f t="shared" si="4"/>
-        <v>513.09530515054587</v>
+        <v>209.95763736740153</v>
       </c>
       <c r="AX12">
         <f t="shared" si="4"/>
-        <v>502.83339904753495</v>
+        <v>205.75848462005351</v>
       </c>
     </row>
     <row r="13" spans="2:50" x14ac:dyDescent="0.2">
@@ -1825,7 +1848,7 @@
         <v>29</v>
       </c>
       <c r="P16" s="2">
-        <f t="shared" ref="P16:T16" si="5">+P3/O3-1</f>
+        <f t="shared" ref="P16:S16" si="5">+P3/O3-1</f>
         <v>1.7187052420510884E-3</v>
       </c>
       <c r="Q16" s="2">
@@ -1849,7 +1872,7 @@
       </c>
       <c r="W16" s="3">
         <f>+NPV(0.08,U12:AX12)</f>
-        <v>7117.5430587853889</v>
+        <v>3326.4737253041526</v>
       </c>
     </row>
     <row r="17" spans="2:23" x14ac:dyDescent="0.2">
@@ -1857,7 +1880,7 @@
         <v>26</v>
       </c>
       <c r="R17" s="2">
-        <f t="shared" ref="R17:T17" si="6">+R5/Q5-1</f>
+        <f t="shared" ref="R17:S17" si="6">+R5/Q5-1</f>
         <v>0.28583935215583134</v>
       </c>
       <c r="S17" s="2">
@@ -1870,7 +1893,7 @@
       </c>
       <c r="W17" s="1">
         <f>+W16-main!L6+main!L7</f>
-        <v>7051.9430587853885</v>
+        <v>3260.8737253041527</v>
       </c>
     </row>
     <row r="18" spans="2:23" x14ac:dyDescent="0.2">
@@ -1878,7 +1901,7 @@
         <v>27</v>
       </c>
       <c r="R18" s="2">
-        <f t="shared" ref="R18:T18" si="7">+R8/Q8-1</f>
+        <f t="shared" ref="R18:S18" si="7">+R8/Q8-1</f>
         <v>0.44381061038219771</v>
       </c>
       <c r="S18" s="2">
@@ -1891,7 +1914,7 @@
       </c>
       <c r="W18">
         <f>+W17/main!L4</f>
-        <v>130.10965053109572</v>
+        <v>60.163721869080305</v>
       </c>
     </row>
     <row r="19" spans="2:23" x14ac:dyDescent="0.2">
@@ -1899,7 +1922,7 @@
         <v>28</v>
       </c>
       <c r="R19" s="2">
-        <f t="shared" ref="R19:T19" si="8">+R11/R10</f>
+        <f t="shared" ref="R19:S19" si="8">+R11/R10</f>
         <v>-0.29063205417607219</v>
       </c>
       <c r="S19" s="2">
@@ -1916,7 +1939,7 @@
         <v>30</v>
       </c>
       <c r="P20" s="2">
-        <f t="shared" ref="P20:T20" si="9">+P12/O12-1</f>
+        <f t="shared" ref="P20:S20" si="9">+P12/O12-1</f>
         <v>0.10190476190476194</v>
       </c>
       <c r="Q20" s="2">
@@ -2150,7 +2173,7 @@
         <v>45</v>
       </c>
       <c r="S42" s="1">
-        <f t="shared" ref="S42:T42" si="10">+S30-S40</f>
+        <f t="shared" ref="S42" si="10">+S30-S40</f>
         <v>1409.4999999999995</v>
       </c>
       <c r="T42" s="1">
@@ -2176,7 +2199,7 @@
         <v>47</v>
       </c>
       <c r="S45" s="2">
-        <f t="shared" ref="S45:T45" si="12">+S12/S30</f>
+        <f t="shared" ref="S45" si="12">+S12/S30</f>
         <v>5.0930670416358785E-2</v>
       </c>
       <c r="T45" s="2">
@@ -2189,7 +2212,7 @@
         <v>48</v>
       </c>
       <c r="S46" s="2">
-        <f t="shared" ref="S46:T46" si="13">+S12/S42</f>
+        <f t="shared" ref="S46" si="13">+S12/S42</f>
         <v>0.15161404753458665</v>
       </c>
       <c r="T46" s="2">
@@ -2289,7 +2312,7 @@
         <v>55</v>
       </c>
       <c r="R54">
-        <f t="shared" ref="R54:T54" si="15">+R48-R49+R50</f>
+        <f t="shared" ref="R54:S54" si="15">+R48-R49+R50</f>
         <v>156.69999999999999</v>
       </c>
       <c r="S54">
@@ -2307,7 +2330,7 @@
       </c>
       <c r="T56">
         <f>+main!L8/model!T54</f>
-        <v>31.0351222253442</v>
+        <v>15.04467547063782</v>
       </c>
     </row>
   </sheetData>
